--- a/globalVariables/globalVarsList_protocolCore.xlsx
+++ b/globalVariables/globalVarsList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\globalVariables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F5339C-0665-495A-85D1-AF573FE754D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D740A0A-928E-4BEE-A3EB-791DC45D20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Var Globali" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Codice Var</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>Var Globale CLOB X3M</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>Patch</t>
+  </si>
+  <si>
+    <t>AGB</t>
   </si>
 </sst>
 </file>
@@ -107,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -134,19 +143,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -168,30 +164,80 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,76 +520,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="8" width="15.5703125" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
+      <c r="J2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
